--- a/reports/wbs.xlsx
+++ b/reports/wbs.xlsx
@@ -1,7 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
+  <fileSharing readOnlyRecommended="1"/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>

--- a/reports/wbs.xlsx
+++ b/reports/wbs.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileSharing readOnlyRecommended="1"/>
   <workbookPr/>
-  <fileSharing readOnlyRecommended="1"/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
